--- a/data/trans_bre/DCD-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Habitat-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,62; 14,26</t>
+          <t>6,7; 14,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,39; 10,01</t>
+          <t>3,71; 10,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4,24; 13,93</t>
+          <t>3,92; 13,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>63,91; 204,19</t>
+          <t>68,15; 196,8</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>38,52; 184,11</t>
+          <t>42,41; 184,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>28,39; 109,46</t>
+          <t>24,31; 104,98</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,58; 12,27</t>
+          <t>6,62; 12,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,94; 8,37</t>
+          <t>2,89; 8,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13,03; 22,19</t>
+          <t>12,93; 21,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>86,14; 236,3</t>
+          <t>80,03; 222,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>36,43; 147,0</t>
+          <t>35,06; 150,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>108,3; 434,49</t>
+          <t>104,55; 406,61</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 12,44</t>
+          <t>5,56; 12,37</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 7,88</t>
+          <t>2,41; 7,95</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 16,49</t>
+          <t>-2,9; 16,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,61; 303,96</t>
+          <t>82,52; 300,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,99; 176,47</t>
+          <t>34,76; 183,64</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 151,69</t>
+          <t>-19,57; 148,04</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,51; 12,19</t>
+          <t>6,74; 12,47</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,7; 10,46</t>
+          <t>4,33; 10,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,26; 14,25</t>
+          <t>5,2; 14,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>86,29; 236,15</t>
+          <t>88,2; 243,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>54,61; 176,24</t>
+          <t>49,75; 175,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>34,52; 111,98</t>
+          <t>33,34; 112,56</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,14; 11,18</t>
+          <t>8,17; 11,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>4,87; 7,76</t>
+          <t>5,04; 8,16</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,5; 14,79</t>
+          <t>7,34; 14,75</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>111,66; 184,5</t>
+          <t>109,54; 185,27</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,08; 129,65</t>
+          <t>67,15; 133,07</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>62,93; 144,25</t>
+          <t>64,03; 146,16</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/DCD-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/DCD-Habitat-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,77</t>
+          <t>11,71</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>6,7; 14,21</t>
+          <t>6,67; 14,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,71; 10,31</t>
+          <t>3,22; 10,18</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,92; 13,79</t>
+          <t>8,23; 15,64</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68,15; 196,8</t>
+          <t>64,05; 202,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>42,41; 184,23</t>
+          <t>37,33; 182,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>24,31; 104,98</t>
+          <t>49,3; 124,51</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>16,75</t>
+          <t>14,54</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>177,88%</t>
+          <t>127,79%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 12,69</t>
+          <t>6,78; 12,18</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,89; 8,6</t>
+          <t>3,02; 8,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12,93; 21,95</t>
+          <t>11,11; 17,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>80,03; 222,48</t>
+          <t>86,86; 221,8</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>35,06; 150,03</t>
+          <t>38,6; 146,76</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>104,55; 406,61</t>
+          <t>85,18; 170,78</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,88</t>
+          <t>15,87</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>134,16%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5,56; 12,37</t>
+          <t>6,07; 12,44</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 7,95</t>
+          <t>2,4; 8,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 16,33</t>
+          <t>12,15; 19,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82,52; 300,0</t>
+          <t>83,88; 273,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>34,76; 183,64</t>
+          <t>34,12; 183,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,57; 148,04</t>
+          <t>86,69; 197,19</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10,87</t>
+          <t>12,88</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>91,41%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,74; 12,47</t>
+          <t>6,85; 12,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,44</t>
+          <t>4,44; 10,45</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,2; 14,48</t>
+          <t>9,84; 16,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>88,2; 243,76</t>
+          <t>88,65; 233,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,75; 175,94</t>
+          <t>53,22; 177,92</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>33,34; 112,56</t>
+          <t>62,82; 131,37</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,99</t>
+          <t>13,83</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>107,38%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>8,17; 11,22</t>
+          <t>8,13; 11,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5,04; 8,16</t>
+          <t>4,82; 7,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,34; 14,75</t>
+          <t>12,25; 15,67</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>109,54; 185,27</t>
+          <t>111,63; 186,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>67,15; 133,07</t>
+          <t>64,34; 125,05</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>64,03; 146,16</t>
+          <t>88,52; 130,46</t>
         </is>
       </c>
     </row>
